--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 10:05</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:24</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>利雅青年</t>
+          <t>利雅得青年</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>布赖合作</t>
+          <t>布赖代合作</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.73/3.56/3.70 让球0</t>
+          <t>SP1.65/3.62/4.05 让球0</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 10:05）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 11:24）</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>新未来SCvs利雅青年</t>
+          <t>新未来SCvs利雅得青年</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>布赖合作vs吉达国民</t>
+          <t>布赖代合作vs吉达国民</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
@@ -1498,19 +1498,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>4.08</t>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.94</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>新未来SCvs利雅青年</t>
+          <t>新未来SCvs利雅得青年</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(45%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>布赖合作vs吉达国民</t>
+          <t>布赖代合作vs吉达国民</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=46%P平=26%P客=28%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=47%P平=26%P客=27%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2154,134 +2154,105 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.73)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>1.41×1.73=2.44</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.73)
-·本菲卡:主胜(1.28)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>1.41×1.73×1.28=3.12</t>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ 核心信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>解读</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>应对</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 核心信号</t>
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>🟢 高信心(7/10+)</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>015/017/023/024/029</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>解读</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>应对</t>
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>🟢 让球SP真实数据</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>全部场次</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>从500.com让球页提取，非估算</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>可用作让球分析</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>🟢 高信心(7/10+)</t>
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>🟡 平局候选</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>015/017/023/024/029</t>
+          <t>004/007/011</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
+          <t>平局概率30-35%，接近主胜</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>作胆材/串关核心</t>
+          <t>双选或慎入</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>🟢 让球SP真实数据</t>
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>🟡 让球数真实</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -2291,54 +2262,10 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>从500.com让球页提取，非估算</t>
+          <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>可用作让球分析</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>🟡 平局候选</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>004/007/011</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>平局概率30-35%，接近主胜</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>双选或慎入</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>🟡 让球数真实</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>全部场次</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>从500.com data-rangqiu提取</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -2352,9 +2279,9 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A50:J50"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A71:J71"/>
     <mergeCell ref="A51:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2384,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>⚽ 周一001 新未来SC vs 利雅青年 [沙职] 00:50</t>
+          <t>⚽ 周一001 新未来SC vs 利雅得青年 [沙特职业联赛] 00:50</t>
         </is>
       </c>
     </row>
@@ -2392,11 +2319,11 @@
       <c r="B4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:50
-联赛：沙职
+联赛：沙特职业联赛
 竞彩SP：1.95 / 3.62 / 2.94
 让球SP(真实)：3.90/3.75/1.65
 差值分析：P主=43% P平=28% P客=29%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2416,7 +2343,7 @@
 竞彩SP：0.00 / 0.00 / 0.00
 让球SP(真实)：暂无
 差值分析：P主=38% P平=31% P客=30%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2424,7 +2351,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>⚽ 周一003 布赖合作 vs 吉达国民 [沙职] 02:00</t>
+          <t>⚽ 周一003 布赖代合作 vs 吉达国民 [沙特职业联赛] 02:00</t>
         </is>
       </c>
     </row>
@@ -2432,11 +2359,11 @@
       <c r="B20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:00
-联赛：沙职
+联赛：沙特职业联赛
 竞彩SP：3.50 / 3.82 / 1.72
 让球SP(真实)：1.89/3.60/3.10
 差值分析：P主=34% P平=28% P客=38%
-推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(43%) 备选半全场:平负
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2454,9 +2381,9 @@
           <t xml:space="preserve">时间：02:45
 联赛：意甲
 竞彩SP：1.41 / 3.90 / 6.10
-让球SP(真实)：2.37/3.30/2.48
+让球SP(真实)：2.42/3.20/2.48
 差值分析：P主=52% P平=26% P客=22%
-推荐：主胜 信心5/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2473,10 +2400,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英超
-竞彩SP：1.73 / 3.56 / 3.70
+竞彩SP：1.65 / 3.62 / 4.05
 让球SP(真实)：暂无
-差值分析：P主=46% P平=26% P客=28%
-推荐：主胜 信心5/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
+差值分析：P主=47% P平=26% P客=27%
+推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2496,7 +2423,7 @@
 竞彩SP：2.22 / 3.10 / 2.81
 让球SP(真实)：4.82/3.85/1.51
 差值分析：P主=40% P平=27% P客=34%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2516,7 +2443,7 @@
 竞彩SP：0.00 / 0.00 / 0.00
 让球SP(真实)：暂无
 差值分析：P主=38% P平=31% P客=32%
-推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2534,9 +2461,9 @@
           <t xml:space="preserve">时间：03:15
 联赛：葡超
 竞彩SP：3.10 / 3.40 / 1.95
-让球SP(真实)：1.64/3.65/4.08
+让球SP(真实)：暂无
 差值分析：P主=36% P平=28% P客=36%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2554,9 +2481,9 @@
           <t xml:space="preserve">时间：03:15
 联赛：葡超
 竞彩SP：1.28 / 4.70 / 7.40
-让球SP(真实)：1.95/3.65/2.92
+让球SP(真实)：1.97/3.55/2.94
 差值分析：P主=54% P平=24% P客=22%
-推荐：主胜 信心5/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2584,7 +2511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2653,89 +2580,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.73)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>5元</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>2.44倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.73)
-·本菲卡:主胜(1.28)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>6元</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>3.12倍</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
@@ -2743,86 +2587,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>61.00</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>61元</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>61.00倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>390.00</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>390元</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>390.00倍</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -2830,130 +2594,10 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>3元</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>3.12倍</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>5元</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>4.84倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>11元</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>10.65倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:24</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 15:19</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.95/3.62/2.94 让球0</t>
+          <t>SP1.95/3.53/3.00 让球0</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.50/3.82/1.72 让球0</t>
+          <t>SP3.70/3.85/1.67 让球0</t>
         </is>
       </c>
     </row>
@@ -895,14 +895,14 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.65/3.62/4.05 让球0</t>
+          <t>SP1.65/3.50/4.20 让球0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>周一007</t>
+          <t>周一006</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>巴列卡诺</t>
+          <t>米尔沃尔</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>赫罗纳</t>
+          <t>赫尔城</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -942,34 +942,34 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP2.22/3.10/2.81 让球0</t>
+          <t>SP1.65/3.42/4.35 让球0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>周一008</t>
+          <t>周一007</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>里奥阿维</t>
+          <t>巴列卡诺</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>里斯本</t>
+          <t>赫罗纳</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>葡超</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -989,14 +989,14 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.22/3.00/2.89 让球0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>周一009</t>
+          <t>周一008</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>阿马多拉</t>
+          <t>里奥阿维</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>法马利康</t>
+          <t>里斯本</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1036,707 +1036,696 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP3.10/3.40/1.95 让球0</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>周一009</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>阿马多拉</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>法马利康</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>SP3.57/3.30/1.83 让球0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>周一010</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>03:15</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>本菲卡</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>布拉加</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>葡超</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>常规赛</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>SP1.28/4.70/7.40 让球0</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 11:24）</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>📊 竞彩SP数据（含真实让球SP · 15:19）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>联赛</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>主vs客</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>胜SP</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>平SP</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>负SP</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>让球</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>让球SP胜</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>让球SP平</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>让球SP负</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>周一001</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>沙特职业联赛</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>新未来SCvs利雅得青年</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D25" s="6" t="n">
         <v>1.95</v>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>周一002</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>瑞超</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>天狼星vs厄格里特</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>周一003</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>沙特职业联赛</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>布赖代合作vs吉达国民</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D27" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>周一004</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>那不勒斯vs博洛尼亚</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>周一005</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>热刺vs利兹联</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E29" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="F29" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>周一004</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>那不勒斯vs博洛尼亚</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>周一006</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>英冠</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>米尔沃尔vs赫尔城</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>周一005</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>热刺vs利兹联</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>周一007</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>巴列卡诺vs赫罗纳</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>周一008</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>里奥阿维vs里斯本</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>暂无</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>周一007</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>巴列卡诺vs赫罗纳</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>周一009</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>阿马多拉vs法马利康</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>周一008</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>周一010</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>葡超</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>里奥阿维vs里斯本</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>本菲卡vs布拉加</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>周一009</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>葡超</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>阿马多拉vs法马利康</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>周一010</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>葡超</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>本菲卡vs布拉加</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>🏆 今晚推荐（按场次顺序）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>对阵</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>信心</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>首选比分</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>备选比分</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>半全场</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>备选半全场</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>仓位</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>周一001</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>新未来SCvs利雅得青年</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>1/10</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>周一002</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>天狼星vs厄格里特</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>1/10</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=38%P平=31%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>周一003</t>
+          <t>周一001</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>布赖代合作vs吉达国民</t>
+          <t>新未来SCvs利雅得青年</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1746,22 +1735,22 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -1771,19 +1760,19 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>周一004</t>
+          <t>周一002</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>那不勒斯vs博洛尼亚</t>
+          <t>天狼星vs厄格里特</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1793,17 +1782,17 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -1823,49 +1812,49 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=52%P平=26%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=38%P平=31%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>周一005</t>
+          <t>周一003</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>热刺vs利兹联</t>
+          <t>布赖代合作vs吉达国民</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1875,19 +1864,19 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=47%P平=26%P客=27%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>周一007</t>
+          <t>周一004</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>巴列卡诺vs赫罗纳</t>
+          <t>那不勒斯vs博洛尼亚</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1897,19 +1886,19 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
@@ -1927,19 +1916,19 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=27%P客=34%|泊松比分2-1|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=52%P平=26%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>周一008</t>
+          <t>周一005</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>里奥阿维vs里斯本</t>
+          <t>热刺vs利兹联</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1949,17 +1938,17 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -1979,19 +1968,19 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=31%P客=32%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=47%P平=26%P客=27%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>周一009</t>
+          <t>周一006</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>阿马多拉vs法马利康</t>
+          <t>米尔沃尔vs赫尔城</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2031,241 +2020,397 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=28%P客=36%|泊松比分2-1|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=45%P平=28%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>周一007</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>巴列卡诺vs赫罗纳</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=40%P平=27%P客=34%|泊松比分2-1|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>周一008</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>里奥阿维vs里斯本</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=38%P平=31%P客=32%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>周一009</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>阿马多拉vs法马利康</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=35%P平=28%P客=36%|泊松比分1-2|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>周一010</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>本菲卡vs布拉加</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=54%P平=24%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>🏆 14场胜负彩（数据源不可用）</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>🔴 14场数据源读取失败: name 'is_banker' is not defined</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="12" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>方案</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>组合场次</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>每场选择</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>注数</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>综合SP</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>⚠️ 核心信号</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>信号</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>应对</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>015/017/023/024/029</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>从500.com让球页提取，非估算</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>可用作让球分析</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>004/007/011</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>平局概率30-35%，接近主胜</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>双选或慎入</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -2275,14 +2420,14 @@
   <mergeCells count="10">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A54:J54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2294,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2320,7 +2465,7 @@
         <is>
           <t xml:space="preserve">时间：00:50
 联赛：沙特职业联赛
-竞彩SP：1.95 / 3.62 / 2.94
+竞彩SP：1.95 / 3.53 / 3.00
 让球SP(真实)：3.90/3.75/1.65
 差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
@@ -2360,9 +2505,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-竞彩SP：3.50 / 3.82 / 1.72
-让球SP(真实)：1.89/3.60/3.10
-差值分析：P主=34% P平=28% P客=38%
+竞彩SP：3.70 / 3.85 / 1.67
+让球SP(真实)：1.91/3.45/3.16
+差值分析：P主=33% P平=28% P客=39%
 推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
@@ -2383,7 +2528,7 @@
 竞彩SP：1.41 / 3.90 / 6.10
 让球SP(真实)：2.42/3.20/2.48
 差值分析：P主=52% P平=26% P客=22%
-推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2400,10 +2545,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英超
-竞彩SP：1.65 / 3.62 / 4.05
-让球SP(真实)：暂无
+竞彩SP：1.65 / 3.50 / 4.20
+让球SP(真实)：3.10/3.32/1.98
 差值分析：P主=47% P平=26% P客=27%
-推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
+推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2411,7 +2556,7 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>⚽ 周一007 巴列卡诺 vs 赫罗纳 [西甲] 03:00</t>
+          <t>⚽ 周一006 米尔沃尔 vs 赫尔城 [英冠] 03:00</t>
         </is>
       </c>
     </row>
@@ -2419,8 +2564,28 @@
       <c r="B44" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
+联赛：英冠
+竞彩SP：1.65 / 3.42 / 4.35
+让球SP(真实)：3.07/3.35/1.98
+差值分析：P主=45% P平=28% P客=27%
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>⚽ 周一007 巴列卡诺 vs 赫罗纳 [西甲] 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="130" customHeight="1">
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：03:00
 联赛：西甲
-竞彩SP：2.22 / 3.10 / 2.81
+竞彩SP：2.22 / 3.00 / 2.89
 让球SP(真实)：4.82/3.85/1.51
 差值分析：P主=40% P平=27% P客=34%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
@@ -2428,15 +2593,15 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>⚽ 周一008 里奥阿维 vs 里斯本 [葡超] 03:15</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="130" customHeight="1">
-      <c r="B52" s="16" t="inlineStr">
+    <row r="60" ht="130" customHeight="1">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
@@ -2448,54 +2613,55 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>⚽ 周一009 阿马多拉 vs 法马利康 [葡超] 03:15</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="130" customHeight="1">
-      <c r="B60" s="16" t="inlineStr">
+    <row r="68" ht="130" customHeight="1">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：3.10 / 3.40 / 1.95
-让球SP(真实)：暂无
-差值分析：P主=36% P平=28% P客=36%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
+竞彩SP：3.57 / 3.30 / 1.83
+让球SP(真实)：1.77/3.40/3.70
+差值分析：P主=35% P平=28% P客=36%
+推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(66%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>⚽ 周一010 本菲卡 vs 布拉加 [葡超] 03:15</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="130" customHeight="1">
-      <c r="B68" s="16" t="inlineStr">
+    <row r="76" ht="130" customHeight="1">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
 竞彩SP：1.28 / 4.70 / 7.40
-让球SP(真实)：1.97/3.55/2.94
+让球SP(真实)：2.00/3.35/3.02
 差值分析：P主=54% P平=24% P客=22%
-推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A75:B75"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A3:B3"/>

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,9 +183,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -194,6 +191,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 15:19</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:52</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.95/3.53/3.00 让球0</t>
+          <t>SP2.03/3.43/2.90 让球0</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.33/4.02/2.22 让球0</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.70/3.85/1.67 让球0</t>
+          <t>SP3.80/3.85/1.65 让球0</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.65/3.42/4.35 让球0</t>
+          <t>SP1.62/3.45/4.50 让球0</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.22/3.00/2.89 让球0</t>
+          <t>SP2.28/2.90/2.89 让球0</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.19/3.80/2.44 让球0</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP3.57/3.30/1.83 让球0</t>
+          <t>SP3.67/3.22/1.83 让球0</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 15:19）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 17:52）</t>
         </is>
       </c>
     </row>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -1256,32 +1256,32 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>2.22</t>
         </is>
       </c>
     </row>
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>3.85</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1317,17 +1317,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.15</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1455,17 +1455,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>2.89</v>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
@@ -1532,32 +1532,32 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>2.44</t>
         </is>
       </c>
     </row>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>1.83</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
@@ -1810,9 +1810,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=38%P平=31%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
@@ -1914,7 +1914,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=52%P平=26%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
@@ -1966,7 +1966,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=47%P平=26%P客=27%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
@@ -2018,7 +2018,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=45%P平=28%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球0=无让球/—</t>
         </is>
@@ -2070,9 +2070,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=40%P平=27%P客=34%|泊松比分2-1|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=39%P平=27%P客=34%|泊松比分2-1|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2122,9 +2122,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=38%P平=31%P客=32%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=41%P平=27%P客=32%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=35%P平=28%P客=36%|泊松比分1-2|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
         </is>
@@ -2226,7 +2226,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J49" s="9" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=54%P平=24%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
@@ -2240,20 +2240,20 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>🔴 14场数据源读取失败: name 'is_banker' is not defined</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="11" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
-      <c r="G54" s="11" t="n"/>
-      <c r="H54" s="11" t="n"/>
-      <c r="I54" s="11" t="n"/>
-      <c r="J54" s="12" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
@@ -2373,7 +2373,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
@@ -2395,7 +2395,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
@@ -2465,8 +2465,8 @@
         <is>
           <t xml:space="preserve">时间：00:50
 联赛：沙特职业联赛
-竞彩SP：1.95 / 3.53 / 3.00
-让球SP(真实)：3.90/3.75/1.65
+竞彩SP：2.03 / 3.43 / 2.90
+让球SP(真实)：4.20/3.75/1.60
 差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让0 无让球=— </t>
@@ -2485,9 +2485,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：瑞超
-竞彩SP：0.00 / 0.00 / 0.00
-让球SP(真实)：暂无
-差值分析：P主=38% P平=31% P客=30%
+竞彩SP：2.33 / 4.02 / 2.22
+让球SP(真实)：2.33/4.02/2.22
+差值分析：P主=38% P平=28% P客=34%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -2505,8 +2505,8 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-竞彩SP：3.70 / 3.85 / 1.67
-让球SP(真实)：1.91/3.45/3.16
+竞彩SP：3.80 / 3.85 / 1.65
+让球SP(真实)：1.93/3.40/3.15
 差值分析：P主=33% P平=28% P客=39%
 推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
 让球:让0 无让球=— </t>
@@ -2546,7 +2546,7 @@
           <t xml:space="preserve">时间：03:00
 联赛：英超
 竞彩SP：1.65 / 3.50 / 4.20
-让球SP(真实)：3.10/3.32/1.98
+让球SP(真实)：3.16/3.25/1.98
 差值分析：P主=47% P平=26% P客=27%
 推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
 让球:让0 无让球=— </t>
@@ -2565,8 +2565,8 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-竞彩SP：1.65 / 3.42 / 4.35
-让球SP(真实)：3.07/3.35/1.98
+竞彩SP：1.62 / 3.45 / 4.50
+让球SP(真实)：3.06/3.25/2.02
 差值分析：P主=45% P平=28% P客=27%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
 让球:让0 无让球=— </t>
@@ -2585,9 +2585,9 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
-竞彩SP：2.22 / 3.00 / 2.89
-让球SP(真实)：4.82/3.85/1.51
-差值分析：P主=40% P平=27% P客=34%
+竞彩SP：2.28 / 2.90 / 2.89
+让球SP(真实)：4.90/4.00/1.48
+差值分析：P主=39% P平=27% P客=34%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -2605,10 +2605,10 @@
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：0.00 / 0.00 / 0.00
-让球SP(真实)：暂无
-差值分析：P主=38% P平=31% P客=32%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+竞彩SP：2.19 / 3.80 / 2.44
+让球SP(真实)：2.19/3.80/2.44
+差值分析：P主=41% P平=27% P客=32%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -2625,7 +2625,7 @@
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：3.57 / 3.30 / 1.83
+竞彩SP：3.67 / 3.22 / 1.83
 让球SP(真实)：1.77/3.40/3.70
 差值分析：P主=35% P平=28% P客=36%
 推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(66%) 备选半全场:平负

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -506,24 +506,24 @@
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 周一竞彩推荐 2026-05-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>📋 周一竞彩推荐 2026-05-11（泊松比分模型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>场次</t>
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>比分</t>
+          <t>比分(备选)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>让球推荐</t>
+          <t>让球</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0(1-1)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>让胜</t>
+          <t>让平</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%平=28%客=28%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=44%平=28%客=28%|泊松λ主=1.8客=1.0|比分1-0|半全场胜胜|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1(1-0)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%平=28%客=34%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=38%平=28%客=34%|泊松λ主=1.4客=1.1|比分2-1|半全场平胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1(1-1)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>让负</t>
+          <t>让平</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%平=27%客=42%|泊松比分1-1|半全场负负|大小球大2.5|让球让负</t>
+          <t>贝叶斯P主=31%平=27%客=42%|泊松λ主=0.9客=1.7|比分0-1|半全场负负|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1(2-1)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>贝叶斯P主=56%平=24%客=20%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=56%平=24%客=20%|泊松λ主=3.3客=1.5|比分3-1|半全场胜胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2(3-1)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>让胜</t>
+          <t>让平</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>贝叶斯P主=48%平=25%客=27%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=48%平=25%客=27%|泊松λ主=3.5客=2.2|比分3-2|半全场胜胜|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2(2-2)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负胜</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>让胜</t>
+          <t>让平</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>贝叶斯P主=47%平=28%客=25%|泊松比分1-1|半全场胜胜|大小球小2.5|让球让胜</t>
+          <t>贝叶斯P主=47%平=28%客=25%|泊松λ主=2.0客=2.1|比分3-2|半全场负胜|大小球小2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2(1-3)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负胜</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>贝叶斯P主=39%平=27%客=34%|泊松比分1-1|半全场胜胜|大小球小2.5|让球让胜</t>
+          <t>贝叶斯P主=39%平=27%客=34%|泊松λ主=1.7客=2.7|比分3-2|半全场负胜|大小球小2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1(1-0)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%平=27%客=32%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=41%平=27%客=32%|泊松λ主=1.5客=1.1|比分2-1|半全场平胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2(1-1)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>让负</t>
+          <t>让平</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%平=27%客=38%|泊松比分1-1|半全场负负|大小球大2.5|让球让负</t>
+          <t>贝叶斯P主=34%平=27%客=38%|泊松λ主=1.7客=2.3|比分1-2|半全场负负|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1(2-1)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>贝叶斯P主=54%平=24%客=22%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=54%平=24%客=22%|泊松λ主=3.3客=1.8|比分3-1|半全场胜胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%平=28%客=28%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=44%平=28%客=28%|泊松λ主=1.8客=1.0|比分1-0|半全场胜胜|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%平=28%客=34%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=38%平=28%客=34%|泊松λ主=1.4客=1.1|比分2-1|半全场平胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%平=27%客=42%|泊松比分1-1|半全场负负|大小球大2.5|让球让负</t>
+          <t>贝叶斯P主=31%平=27%客=42%|泊松λ主=0.9客=1.7|比分0-1|半全场负负|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=56%平=24%客=20%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=56%平=24%客=20%|泊松λ主=3.3客=1.5|比分3-1|半全场胜胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=48%平=25%客=27%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=48%平=25%客=27%|泊松λ主=3.5客=2.2|比分3-2|半全场胜胜|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=47%平=28%客=25%|泊松比分1-1|半全场胜胜|大小球小2.5|让球让胜</t>
+          <t>贝叶斯P主=47%平=28%客=25%|泊松λ主=2.0客=2.1|比分3-2|半全场负胜|大小球小2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=39%平=27%客=34%|泊松比分1-1|半全场胜胜|大小球小2.5|让球让胜</t>
+          <t>贝叶斯P主=39%平=27%客=34%|泊松λ主=1.7客=2.7|比分3-2|半全场负胜|大小球小2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%平=27%客=32%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=41%平=27%客=32%|泊松λ主=1.5客=1.1|比分2-1|半全场平胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%平=27%客=38%|泊松比分1-1|半全场负负|大小球大2.5|让球让负</t>
+          <t>贝叶斯P主=34%平=27%客=38%|泊松λ主=1.7客=2.3|比分1-2|半全场负负|大小球大2.5|让球让平</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=54%平=24%客=22%|泊松比分1-1|半全场胜胜|大小球大2.5|让球让胜</t>
+          <t>贝叶斯P主=54%平=24%客=22%|泊松λ主=3.3客=1.8|比分3-1|半全场胜胜|大小球大2.5|让球让胜</t>
         </is>
       </c>
     </row>
@@ -1477,8 +1477,8 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>投注金额</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:11</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:33</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 22:11）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 22:33）</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,16 +139,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:33</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:51</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP2.03/3.43/2.90 让球0</t>
+          <t>SP4.20/3.75/1.60 让球0</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.33/4.02/2.22 让球0</t>
+          <t>SP2.27/4.02/2.27 让球0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.80/3.85/1.65 让球0</t>
+          <t>SP1.98/3.35/3.08 让球0</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP1.41/3.90/6.10 让球0</t>
+          <t>SP2.48/3.10/2.48 让球0</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.65/3.50/4.20 让球0</t>
+          <t>SP3.30/3.10/1.99 让球0</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.62/3.45/4.50 让球0</t>
+          <t>SP3.19/3.05/2.05 让球0</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.28/2.90/2.89 让球0</t>
+          <t>SP5.40/4.10/1.43 让球0</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.19/3.80/2.44 让球0</t>
+          <t>SP2.28/3.70/2.38 让球0</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP3.67/3.22/1.83 让球0</t>
+          <t>SP1.62/3.65/4.20 让球0</t>
         </is>
       </c>
     </row>
@@ -1082,14 +1082,14 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP1.28/4.70/7.40 让球0</t>
+          <t>SP2.04/3.25/3.02 让球0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 22:33）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 22:51）</t>
         </is>
       </c>
     </row>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -1208,32 +1208,32 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>4.02</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>2.22</t>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3.8</v>
+        <v>1.98</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.65</v>
+        <v>3.08</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1269,17 +1269,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.41</v>
+        <v>2.48</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>6.1</v>
+        <v>2.48</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1315,17 +1315,17 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>6.40</t>
         </is>
       </c>
     </row>
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>4.15</t>
         </is>
       </c>
     </row>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.62</v>
+        <v>3.19</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2.89</v>
+        <v>1.43</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.82</t>
         </is>
       </c>
     </row>
@@ -1484,32 +1484,32 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>2.44</t>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3.67</v>
+        <v>1.62</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7.4</v>
+        <v>3.02</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.40</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -1710,9 +1710,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1791,22 +1791,22 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1814,9 +1814,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(42%)|让球0=无让球/—</t>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=38%P平=32%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1866,9 +1866,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=52%P平=26%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1885,32 +1885,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -1918,9 +1918,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=47%P平=26%P客=27%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=34%P平=31%P客=35%|泊松比分2-3|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1970,9 +1970,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=45%P平=28%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球0=无让球/—</t>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=34%P平=31%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(65%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -2022,9 +2022,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=39%P平=27%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球0=无让球/—</t>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=35%P平=27%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2074,9 +2074,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=41%P平=27%P客=32%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>胜负</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -2126,9 +2126,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分1-2|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=33%P平=33%P客=34%|泊松比分1-2|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2178,9 +2178,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=54%P平=24%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=41%P平=28%P客=30%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2244,52 +2244,52 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>英超</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>曼彻斯特城</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>水晶宫</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>4.9/10</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>★胆</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>P主=49%</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -2348,52 +2348,52 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>西班牙人</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>毕尔巴鄂竞技</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>4.1/10</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>★胆</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>P主=46%</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
+      <c r="J57" s="10" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -2979,63 +2979,63 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   1. 主胜           (信心4.9/10)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   3. 主胜           (信心4.1/10)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   5. 客胜/平局        (信心3.8/10)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   4. 主胜/平局        (信心3.7/10)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   7. 主胜/平局        (信心3.7/10)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   8. 主胜/平局        (信心3.7/10)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   9. 主胜/平局        (信心3.6/10)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  11. 主胜/平局        (信心3.6/10)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  10. 主胜/平局        (信心3.5/10)</t>
         </is>
@@ -3078,134 +3078,105 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.65)</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>1.41×1.65=2.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.65)
-·本菲卡:主胜(1.28)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>1.41×1.65×1.28=2.98</t>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ 核心信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>解读</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>应对</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 核心信号</t>
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>🟢 高信心(4/10+)</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>0场贝叶斯概率最高</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>解读</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>应对</t>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>🟢 让球SP真实数据</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>全部场次</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>从500.com让球页提取，非估算</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>可用作让球分析</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>🟢 高信心(4/10+)</t>
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>🟡 平局候选</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>周一004/周一005/周一010</t>
+          <t>周一003/周一004/周一005/周一006/周一009</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>3场贝叶斯概率最高</t>
+          <t>5场平局概率30%+</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>作胆材/串关核心</t>
+          <t>双选或慎入</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>🟢 让球SP真实数据</t>
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>🟡 让球数真实</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -3215,54 +3186,10 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>从500.com让球页提取，非估算</t>
+          <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>可用作让球分析</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>🟡 平局候选</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>0场平局概率30%+</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>双选或慎入</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>🟡 让球数真实</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>全部场次</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>从500.com data-rangqiu提取</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -3280,8 +3207,8 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A88:J88"/>
     <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A75:J75"/>
     <mergeCell ref="A74:J74"/>
@@ -3326,10 +3253,10 @@
         <is>
           <t xml:space="preserve">时间：00:50
 联赛：沙特职业联赛
-竞彩SP：2.03 / 3.43 / 2.90
-让球SP(真实)：4.20/3.75/1.60
-差值分析：P主=43% P平=28% P客=29%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+竞彩SP：4.20 / 3.75 / 1.60
+让球SP(真实)：2.06/3.34/2.90
+差值分析：P主=38% P平=29% P客=33%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(41%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3346,8 +3273,8 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：瑞超
-竞彩SP：2.33 / 4.02 / 2.22
-让球SP(真实)：2.33/4.02/2.22
+竞彩SP：2.27 / 4.02 / 2.27
+让球SP(真实)：暂无
 差值分析：P主=38% P平=28% P客=34%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
@@ -3366,10 +3293,10 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-竞彩SP：3.80 / 3.85 / 1.65
-让球SP(真实)：1.93/3.40/3.15
-差值分析：P主=33% P平=28% P客=39%
-推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
+竞彩SP：1.98 / 3.35 / 3.08
+让球SP(真实)：3.92/3.90/1.62
+差值分析：P主=38% P平=32% P客=30%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3386,10 +3313,10 @@
         <is>
           <t xml:space="preserve">时间：02:45
 联赛：意甲
-竞彩SP：1.41 / 3.90 / 6.10
-让球SP(真实)：2.42/3.20/2.48
-差值分析：P主=52% P平=26% P客=22%
-推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+竞彩SP：2.48 / 3.10 / 2.48
+让球SP(真实)：1.39/3.95/6.40
+差值分析：P主=37% P平=30% P客=33%
+推荐：主胜 信心1/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3406,10 +3333,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英超
-竞彩SP：1.65 / 3.50 / 4.20
-让球SP(真实)：3.16/3.25/1.98
-差值分析：P主=47% P平=26% P客=27%
-推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:平胜
+竞彩SP：3.30 / 3.10 / 1.99
+让球SP(真实)：1.64/3.60/4.15
+差值分析：P主=34% P平=31% P客=35%
+推荐：客胜 信心1/10 比分2-3(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3426,10 +3353,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-竞彩SP：1.62 / 3.45 / 4.50
-让球SP(真实)：3.06/3.25/2.02
-差值分析：P主=45% P平=28% P客=27%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
+竞彩SP：3.19 / 3.05 / 2.05
+让球SP(真实)：1.60/3.45/4.65
+差值分析：P主=34% P平=31% P客=34%
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(65%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3446,10 +3373,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
-竞彩SP：2.28 / 2.90 / 2.89
-让球SP(真实)：4.90/4.00/1.48
-差值分析：P主=39% P平=27% P客=34%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
+竞彩SP：5.40 / 4.10 / 1.43
+让球SP(真实)：2.36/2.85/2.82
+差值分析：P主=35% P平=27% P客=37%
+推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(68%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3466,9 +3393,9 @@
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：2.19 / 3.80 / 2.44
-让球SP(真实)：2.19/3.80/2.44
-差值分析：P主=41% P平=27% P客=32%
+竞彩SP：2.28 / 3.70 / 2.38
+让球SP(真实)：暂无
+差值分析：P主=40% P平=27% P客=33%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -3486,10 +3413,10 @@
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：3.67 / 3.22 / 1.83
-让球SP(真实)：1.77/3.40/3.70
-差值分析：P主=34% P平=28% P客=38%
-推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(66%) 备选半全场:平负
+竞彩SP：1.62 / 3.65 / 4.20
+让球SP(真实)：3.38/3.08/1.97
+差值分析：P主=33% P平=33% P客=34%
+推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(66%) 备选半全场:胜负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3506,10 +3433,10 @@
         <is>
           <t xml:space="preserve">时间：03:15
 联赛：葡超
-竞彩SP：1.28 / 4.70 / 7.40
-让球SP(真实)：2.00/3.35/3.02
-差值分析：P主=54% P平=24% P客=22%
-推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+竞彩SP：2.04 / 3.25 / 3.02
+让球SP(真实)：1.28/4.70/7.40
+差值分析：P主=41% P平=28% P客=30%
+推荐：主胜 信心1/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3538,7 +3465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3607,89 +3534,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.65)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>5元</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>2.33倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>·那不勒斯:主胜(1.41)
-·热刺:主胜(1.65)
-·本菲卡:主胜(1.28)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>6元</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>2.98倍</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
@@ -3697,86 +3541,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>58元</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>58.00倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>372.00</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>372元</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>372.00倍</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
@@ -3784,130 +3548,10 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>3元</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2.98倍</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>5元</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>4.84倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>周一004+周一005+周一010</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>11元</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>10.65倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:51</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:14</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 22:51）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 23:14）</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(41%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=32%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=32%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=40%P平=28%P客=32%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=31%P客=35%|泊松比分2-3|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=35%P平=29%P客=36%|泊松比分2-3|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=31%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(65%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(65%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=27%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=27%P平=24%P客=49%|泊松比分1-2|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -2103,22 +2103,22 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>胜负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=33%P平=33%P客=34%|泊松比分1-2|半全场负负|大小球大2.5(66%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%P平=28%P客=30%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=45%P平=28%P客=28%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>周一003/周一004/周一005/周一006/周一009</t>
+          <t>周一006</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>5场平局概率30%+</t>
+          <t>1场平局概率30%+</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3255,8 +3255,8 @@
 联赛：沙特职业联赛
 竞彩SP：4.20 / 3.75 / 1.60
 让球SP(真实)：2.06/3.34/2.90
-差值分析：P主=38% P平=29% P客=33%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(41%) 备选半全场:平胜
+差值分析：P主=32% P平=28% P客=39%
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3295,7 +3295,7 @@
 联赛：沙特职业联赛
 竞彩SP：1.98 / 3.35 / 3.08
 让球SP(真实)：3.92/3.90/1.62
-差值分析：P主=38% P平=32% P客=30%
+差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -3315,7 +3315,7 @@
 联赛：意甲
 竞彩SP：2.48 / 3.10 / 2.48
 让球SP(真实)：1.39/3.95/6.40
-差值分析：P主=37% P平=30% P客=33%
+差值分析：P主=40% P平=28% P客=32%
 推荐：主胜 信心1/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -3335,7 +3335,7 @@
 联赛：英超
 竞彩SP：3.30 / 3.10 / 1.99
 让球SP(真实)：1.64/3.60/4.15
-差值分析：P主=34% P平=31% P客=35%
+差值分析：P主=35% P平=29% P客=36%
 推荐：客胜 信心1/10 比分2-3(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
@@ -3355,7 +3355,7 @@
 联赛：英冠
 竞彩SP：3.19 / 3.05 / 2.05
 让球SP(真实)：1.60/3.45/4.65
-差值分析：P主=34% P平=31% P客=34%
+差值分析：P主=36% P平=30% P客=34%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(65%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
@@ -3375,8 +3375,8 @@
 联赛：西甲
 竞彩SP：5.40 / 4.10 / 1.43
 让球SP(真实)：2.36/2.85/2.82
-差值分析：P主=35% P平=27% P客=37%
-推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(68%) 备选半全场:平负
+差值分析：P主=27% P平=24% P客=49%
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(68%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3415,8 +3415,8 @@
 联赛：葡超
 竞彩SP：1.62 / 3.65 / 4.20
 让球SP(真实)：3.38/3.08/1.97
-差值分析：P主=33% P平=33% P客=34%
-推荐：客胜 信心1/10 比分1-2(泊松) 半全场负负 大小球大2.5(66%) 备选半全场:胜负
+差值分析：P主=44% P平=27% P客=29%
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3435,8 +3435,8 @@
 联赛：葡超
 竞彩SP：2.04 / 3.25 / 3.02
 让球SP(真实)：1.28/4.70/7.40
-差值分析：P主=41% P平=28% P客=30%
-推荐：主胜 信心1/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+差值分析：P主=45% P平=28% P客=28%
+推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>

--- a/Aii竞彩推荐_2026-05-11.xlsx
+++ b/Aii竞彩推荐_2026-05-11.xlsx
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:14</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:25</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP4.20/3.75/1.60 让球0</t>
+          <t>SP4.20/3.75/1.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.27/4.02/2.27 让球0</t>
+          <t>SP2.27/4.02/2.27 让球-2</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.98/3.35/3.08 让球0</t>
+          <t>SP1.98/3.35/3.08 让球+1</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP2.48/3.10/2.48 让球0</t>
+          <t>SP2.48/3.10/2.48 让球-1</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP3.30/3.10/1.99 让球0</t>
+          <t>SP3.30/3.10/1.99 让球-1</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP3.19/3.05/2.05 让球0</t>
+          <t>SP3.19/3.05/2.05 让球-1</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP5.40/4.10/1.43 让球0</t>
+          <t>SP5.40/4.10/1.43 让球-1</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.28/3.70/2.38 让球0</t>
+          <t>SP2.28/3.70/2.38 让球+2</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP1.62/3.65/4.20 让球0</t>
+          <t>SP1.62/3.65/4.20 让球+1</t>
         </is>
       </c>
     </row>
@@ -1082,14 +1082,14 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP2.04/3.25/3.02 让球0</t>
+          <t>SP2.04/3.25/3.02 让球-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 23:14）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 23:25）</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=32%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=32%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-2=输盘/让胜⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=28%P客=32%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=40%P平=28%P客=32%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=29%P客=36%|泊松比分2-3|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=35%P平=29%P客=36%|泊松比分2-3|半全场负负|大小球大2.5(72%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(65%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(65%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=27%P平=24%P客=49%|泊松比分1-2|半全场负负|大小球大2.5(68%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=27%P平=24%P客=49%|泊松比分1-2|半全场负负|大小球大2.5(68%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+2=输盘/让负</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(66%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=45%P平=28%P客=28%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=45%P平=28%P客=28%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
 让球SP(真实)：2.06/3.34/2.90
 差值分析：P主=32% P平=28% P客=39%
 推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让0 无让球=— </t>
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3271,13 +3271,13 @@
     <row r="12" ht="130" customHeight="1">
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：01:00
+          <t>时间：01:00
 联赛：瑞超
 竞彩SP：2.27 / 4.02 / 2.27
 让球SP(真实)：暂无
 差值分析：P主=38% P平=28% P客=34%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
 让球SP(真实)：3.92/3.90/1.62
 差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
 让球SP(真实)：1.39/3.95/6.40
 差值分析：P主=40% P平=28% P客=32%
 推荐：主胜 信心1/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
 让球SP(真实)：1.64/3.60/4.15
 差值分析：P主=35% P平=29% P客=36%
 推荐：客胜 信心1/10 比分2-3(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
-让球:让0 无让球=— </t>
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
 让球SP(真实)：1.60/3.45/4.65
 差值分析：P主=36% P平=30% P客=34%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(65%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
 让球SP(真实)：2.36/2.85/2.82
 差值分析：P主=27% P平=24% P客=49%
 推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(68%) 备选半全场:平负
-让球:让0 无让球=— </t>
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
 让球SP(真实)：暂无
 差值分析：P主=40% P平=27% P客=33%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让+2 输盘=让负 </t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
 让球SP(真实)：3.38/3.08/1.97
 差值分析：P主=44% P平=27% P客=29%
 推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(66%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
 让球SP(真实)：1.28/4.70/7.40
 差值分析：P主=45% P平=28% P客=28%
 推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
